--- a/Мечты и не только.xlsx
+++ b/Мечты и не только.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>Баги</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t>Домашняя страница с последними, рекомендуемыми и/или популярными действиями и каким-то общим превью коллекции</t>
+  </si>
+  <si>
+    <t>переместить вин чуз директ на фронтенд</t>
+  </si>
+  <si>
+    <t>открытие в… по даблклику в коллекции</t>
   </si>
 </sst>
 </file>
@@ -297,7 +303,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,6 +334,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -434,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -497,6 +509,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -934,8 +949,14 @@
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
+      <c r="E9" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="F9" s="10" t="s">
         <v>9</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>81</v>
       </c>
       <c r="I9" s="21" t="s">
         <v>30</v>
